--- a/PTE RS_WFD.xlsx
+++ b/PTE RS_WFD.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rr/github_repo/EnglishSummary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D962C0-4847-694D-A16E-E6AC4BEBD575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D88C7D-336A-8947-8D08-B0EEA7A89F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="700" windowWidth="16220" windowHeight="13480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3460" yWindow="700" windowWidth="16220" windowHeight="13480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="8" r:id="rId1"/>
-    <sheet name="DI" sheetId="6" r:id="rId2"/>
-    <sheet name="DI 图片题素材" sheetId="29" r:id="rId3"/>
-    <sheet name="SWT" sheetId="4" r:id="rId4"/>
-    <sheet name="WE素材" sheetId="17" r:id="rId5"/>
-    <sheet name="易混单词--已复制" sheetId="18" state="hidden" r:id="rId6"/>
-    <sheet name="记不住单词--已复制" sheetId="28" state="hidden" r:id="rId7"/>
-    <sheet name="RA发音纠正--已复制指单词发音解析" sheetId="7" state="hidden" r:id="rId8"/>
-    <sheet name="FIB易混单词--已复制" sheetId="15" state="hidden" r:id="rId9"/>
-    <sheet name="FIB固定搭配--已复制" sheetId="26" state="hidden" r:id="rId10"/>
+    <sheet name="RA 注意事项" sheetId="30" r:id="rId2"/>
+    <sheet name="DI" sheetId="6" r:id="rId3"/>
+    <sheet name="DI 图片题素材" sheetId="29" r:id="rId4"/>
+    <sheet name="SWT" sheetId="4" r:id="rId5"/>
+    <sheet name="WE素材" sheetId="17" r:id="rId6"/>
+    <sheet name="易混单词--已复制" sheetId="18" state="hidden" r:id="rId7"/>
+    <sheet name="记不住单词--已复制" sheetId="28" state="hidden" r:id="rId8"/>
+    <sheet name="RA发音纠正--已复制指单词发音解析" sheetId="7" state="hidden" r:id="rId9"/>
+    <sheet name="FIB易混单词--已复制" sheetId="15" state="hidden" r:id="rId10"/>
+    <sheet name="FIB固定搭配--已复制" sheetId="26" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FIB易混单词--已复制'!$A$8:$E$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'易混单词--已复制'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'FIB易混单词--已复制'!$A$8:$E$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'易混单词--已复制'!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="1759">
   <si>
     <t>Hello, This  is Guannan Ruan</t>
   </si>
@@ -7799,13 +7800,129 @@
   </si>
   <si>
     <t>丹</t>
+  </si>
+  <si>
+    <t>合理的断句</t>
+  </si>
+  <si>
+    <t>发音果断清晰，不要拖音粘连</t>
+  </si>
+  <si>
+    <t>音调往下沉</t>
+  </si>
+  <si>
+    <t>that</t>
+  </si>
+  <si>
+    <t>做从句主语时，断在that前</t>
+  </si>
+  <si>
+    <t>做从句标识时，断在that后</t>
+  </si>
+  <si>
+    <t>介词前一搬有断句</t>
+  </si>
+  <si>
+    <t>a.</t>
+  </si>
+  <si>
+    <t>b.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c. </t>
+  </si>
+  <si>
+    <t>主语</t>
+  </si>
+  <si>
+    <t>d.</t>
+  </si>
+  <si>
+    <t>定语从句前面与修饰词可以相连，从句结束处可以划分为一个意群</t>
+  </si>
+  <si>
+    <t>避免语调奇怪</t>
+  </si>
+  <si>
+    <t>正常说话语调即可</t>
+  </si>
+  <si>
+    <t>e.</t>
+  </si>
+  <si>
+    <r>
+      <t>有介词修饰时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>断句</t>
+    </r>
+  </si>
+  <si>
+    <t>不要懒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refer </t>
+  </si>
+  <si>
+    <t>https://www.ptexj.com/zh-CN/practice/read_alouds/171</t>
+  </si>
+  <si>
+    <t>RA#171 猩际自研口语评分系统，小猩 RA 一句话 测试版 智能评分 78/90 https://www.ptexj.com/zh-CN/practice/answer_item?model=read_alouds&amp;answer_id=2492372731</t>
+  </si>
+  <si>
+    <t>and 连接的两个词</t>
+  </si>
+  <si>
+    <t>可以在and前小段一下</t>
+  </si>
+  <si>
+    <t>是代词或的那个单词时，与动词相连</t>
+  </si>
+  <si>
+    <t>是实词词组，可单独做意群</t>
+  </si>
+  <si>
+    <t>商场顾客</t>
+  </si>
+  <si>
+    <t>sale clerks</t>
+  </si>
+  <si>
+    <t>售货员</t>
+  </si>
+  <si>
+    <t>belt</t>
+  </si>
+  <si>
+    <t>stem</t>
+  </si>
+  <si>
+    <t>茎</t>
+  </si>
+  <si>
+    <t>/stem/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7893,6 +8010,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -7917,10 +8042,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -7962,8 +8088,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -8284,6 +8413,2261 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:E214"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="26.5" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>955</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D70" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D73" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D76" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D83" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A95" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A97" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A101" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D160" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A165" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A167" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A168" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A170" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A171" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A172" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A173" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A174" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A175" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A177" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A178" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A179" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A180" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A182" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D187" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D197" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A202" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A203" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A204" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A205" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A206" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A207" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A208" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A209" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A210" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A212" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A213" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A214" s="1" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:E136" xr:uid="{00000000-0001-0000-1600-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:E136">
+    <sortCondition ref="A9:A58"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBD7C48-68A5-A546-9902-757676FC1C71}">
   <dimension ref="A2:C59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8775,6 +11159,132 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C742873F-BC9E-4D42-900E-A7D04478847B}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="9" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="9" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D11" r:id="rId1" xr:uid="{3E0AE948-2378-AF40-B155-E686D83395ED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8970,9 +11480,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4745B318-B4FC-EE4E-B419-78F745D8E788}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -9070,6 +11580,17 @@
         <v>1649</v>
       </c>
     </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1758</v>
+      </c>
+    </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>1650</v>
@@ -9314,6 +11835,24 @@
       </c>
       <c r="C51" t="s">
         <v>1726</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>1755</v>
       </c>
     </row>
   </sheetData>
@@ -9321,7 +11860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9419,7 +11958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9465,7 +12004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10831,7 +13370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A1136F-872F-C743-A77D-7C6CCADE4BFE}">
   <dimension ref="A1:V84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -12274,7 +14813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -13035,2259 +15574,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:E214"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="26.5" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="24" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>810</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>955</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>811</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1619</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>1620</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>1622</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1623</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>1626</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>1627</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>828</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>837</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D70" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>865</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D76" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>867</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D83" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>898</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>900</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
-        <v>904</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>922</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
-        <v>928</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
-        <v>930</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A101" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>943</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A111" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>958</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>965</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A119" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>994</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
-        <v>996</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A126" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A127" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="1" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A130" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A131" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A132" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A133" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A134" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A135" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A136" s="1" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A138" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A139" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A140" s="1" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D160" s="1" t="s">
-        <v>1382</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161" s="1" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165" s="1" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A180" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A182" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A183" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A184" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A185" s="4" t="s">
-        <v>1227</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A186" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D187" s="1" t="s">
-        <v>1271</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A188" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189" s="1" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190" s="1" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="1" t="s">
-        <v>1363</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195" s="1" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196" s="1" t="s">
-        <v>1397</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D197" s="1" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198" s="1" t="s">
-        <v>1402</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>1404</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199" s="1" t="s">
-        <v>1422</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200" s="1" t="s">
-        <v>934</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>1434</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201" s="1" t="s">
-        <v>1438</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>1440</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202" s="1" t="s">
-        <v>1450</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>1451</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>1452</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203" s="1" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>1455</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204" s="1" t="s">
-        <v>1464</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>1465</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>1466</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205" s="1" t="s">
-        <v>1468</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A206" s="1" t="s">
-        <v>1476</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>1478</v>
-      </c>
-      <c r="E206" s="1" t="s">
-        <v>1479</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
-        <v>1482</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>1484</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>1486</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A209" s="1" t="s">
-        <v>1489</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>1490</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A210" s="1" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A211" s="4" t="s">
-        <v>1515</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>1517</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>1518</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>1524</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213" s="1" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>1597</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>1599</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>1610</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A8:E136" xr:uid="{00000000-0001-0000-1600-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:E136">
-    <sortCondition ref="A9:A58"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>